--- a/data/信用债发行汇总_2026-08-11.xlsx
+++ b/data/信用债发行汇总_2026-08-11.xlsx
@@ -1154,7 +1154,11 @@
           <t>26金融街MTN004B</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>102683031.IB</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -1334,7 +1338,11 @@
           <t>26金融街MTN004A</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>102683030.IB</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2+2</t>
